--- a/artfynd/A 20804-2026 artfynd.xlsx
+++ b/artfynd/A 20804-2026 artfynd.xlsx
@@ -2076,45 +2076,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134225059</v>
+        <v>134217628</v>
       </c>
       <c r="B15" t="n">
-        <v>91968</v>
+        <v>57153</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1205</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lång-Mjösjön, Ång</t>
+          <t>Lång Mjösjön, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>652887</v>
+        <v>652709</v>
       </c>
       <c r="R15" t="n">
-        <v>7004339</v>
+        <v>7004397</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2144,9 +2152,19 @@
           <t>2026-06-07</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2161,60 +2179,63 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Markus Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134225057</v>
+        <v>134217645</v>
       </c>
       <c r="B16" t="n">
-        <v>79358</v>
+        <v>92389</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lång-Mjösjön, Ång</t>
+          <t>Lång Mjösjön, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>652962</v>
+        <v>652909</v>
       </c>
       <c r="R16" t="n">
-        <v>7004432</v>
+        <v>7004298</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2241,36 +2262,47 @@
           <t>2026-06-07</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134217628</v>
+        <v>134217644</v>
       </c>
       <c r="B17" t="n">
         <v>57153</v>
@@ -2298,28 +2330,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lång Mjösjön, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>652709</v>
+        <v>652907</v>
       </c>
       <c r="R17" t="n">
-        <v>7004397</v>
+        <v>7004308</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2348,7 +2384,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2358,7 +2394,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2378,58 +2414,55 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134217645</v>
+        <v>134225059</v>
       </c>
       <c r="B18" t="n">
-        <v>92389</v>
+        <v>91968</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>1205</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lång Mjösjön, Ång</t>
+          <t>Lång-Mjösjön, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>652909</v>
+        <v>652887</v>
       </c>
       <c r="R18" t="n">
-        <v>7004298</v>
+        <v>7004339</v>
       </c>
       <c r="S18" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2456,50 +2489,39 @@
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134217644</v>
+        <v>134225057</v>
       </c>
       <c r="B19" t="n">
-        <v>57153</v>
+        <v>79358</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2507,46 +2529,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lång Mjösjön, Ång</t>
+          <t>Lång-Mjösjön, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>652907</v>
+        <v>652962</v>
       </c>
       <c r="R19" t="n">
-        <v>7004308</v>
+        <v>7004432</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -2576,19 +2586,9 @@
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>12:02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2603,12 +2603,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 20804-2026 artfynd.xlsx
+++ b/artfynd/A 20804-2026 artfynd.xlsx
@@ -2076,53 +2076,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134217628</v>
+        <v>134225059</v>
       </c>
       <c r="B15" t="n">
-        <v>57153</v>
+        <v>91968</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>1205</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lång Mjösjön, Ång</t>
+          <t>Lång-Mjösjön, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>652709</v>
+        <v>652887</v>
       </c>
       <c r="R15" t="n">
-        <v>7004397</v>
+        <v>7004339</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2152,19 +2144,9 @@
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>10:04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2179,63 +2161,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134217645</v>
+        <v>134225057</v>
       </c>
       <c r="B16" t="n">
-        <v>92389</v>
+        <v>79358</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lång Mjösjön, Ång</t>
+          <t>Lång-Mjösjön, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>652909</v>
+        <v>652962</v>
       </c>
       <c r="R16" t="n">
-        <v>7004298</v>
+        <v>7004432</v>
       </c>
       <c r="S16" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2262,47 +2241,36 @@
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134217644</v>
+        <v>134217628</v>
       </c>
       <c r="B17" t="n">
         <v>57153</v>
@@ -2330,32 +2298,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lång Mjösjön, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>652907</v>
+        <v>652709</v>
       </c>
       <c r="R17" t="n">
-        <v>7004308</v>
+        <v>7004397</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2384,7 +2348,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2394,7 +2358,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2414,55 +2378,58 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134225059</v>
+        <v>134217645</v>
       </c>
       <c r="B18" t="n">
-        <v>91968</v>
+        <v>92389</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1205</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lång-Mjösjön, Ång</t>
+          <t>Lång Mjösjön, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>652887</v>
+        <v>652909</v>
       </c>
       <c r="R18" t="n">
-        <v>7004339</v>
+        <v>7004298</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2489,39 +2456,50 @@
           <t>2026-06-07</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134225057</v>
+        <v>134217644</v>
       </c>
       <c r="B19" t="n">
-        <v>79358</v>
+        <v>57153</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2529,34 +2507,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lång-Mjösjön, Ång</t>
+          <t>Lång Mjösjön, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>652962</v>
+        <v>652907</v>
       </c>
       <c r="R19" t="n">
-        <v>7004432</v>
+        <v>7004308</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -2586,9 +2576,19 @@
           <t>2026-06-07</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2603,12 +2603,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 20804-2026 artfynd.xlsx
+++ b/artfynd/A 20804-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>134217631</v>
       </c>
       <c r="B3" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>134217635</v>
       </c>
       <c r="B4" t="n">
-        <v>80484</v>
+        <v>80485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>134217642</v>
       </c>
       <c r="B5" t="n">
-        <v>91920</v>
+        <v>91922</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>134225062</v>
       </c>
       <c r="B6" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>134225053</v>
       </c>
       <c r="B8" t="n">
-        <v>80484</v>
+        <v>80485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>134217633</v>
       </c>
       <c r="B9" t="n">
-        <v>98043</v>
+        <v>98045</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>134217641</v>
       </c>
       <c r="B10" t="n">
-        <v>92389</v>
+        <v>92391</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,51 +1646,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134217640</v>
+        <v>134225052</v>
       </c>
       <c r="B11" t="n">
-        <v>91957</v>
+        <v>80485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lång Mjösjön, Ång</t>
+          <t>Lång-Mjösjön, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>652885</v>
+        <v>652787</v>
       </c>
       <c r="R11" t="n">
-        <v>7004317</v>
+        <v>7004521</v>
       </c>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1717,50 +1714,39 @@
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134217636</v>
+        <v>134217640</v>
       </c>
       <c r="B12" t="n">
-        <v>57972</v>
+        <v>91959</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1768,31 +1754,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1800,13 +1781,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>652793</v>
+        <v>652885</v>
       </c>
       <c r="R12" t="n">
-        <v>7004452</v>
+        <v>7004317</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1835,7 +1816,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1845,7 +1826,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1854,6 +1835,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1865,55 +1847,63 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134225052</v>
+        <v>134217636</v>
       </c>
       <c r="B13" t="n">
-        <v>80484</v>
+        <v>57972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lång-Mjösjön, Ång</t>
+          <t>Lång Mjösjön, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>652787</v>
+        <v>652793</v>
       </c>
       <c r="R13" t="n">
-        <v>7004521</v>
+        <v>7004452</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1940,9 +1930,19 @@
           <t>2026-06-07</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1957,12 +1957,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1972,7 +1972,7 @@
         <v>134217638</v>
       </c>
       <c r="B14" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2076,32 +2076,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134225059</v>
+        <v>134225057</v>
       </c>
       <c r="B15" t="n">
-        <v>91968</v>
+        <v>79359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>652887</v>
+        <v>652962</v>
       </c>
       <c r="R15" t="n">
-        <v>7004339</v>
+        <v>7004432</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2173,32 +2173,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134225057</v>
+        <v>134225059</v>
       </c>
       <c r="B16" t="n">
-        <v>79358</v>
+        <v>91970</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,13 +2208,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>652962</v>
+        <v>652887</v>
       </c>
       <c r="R16" t="n">
-        <v>7004432</v>
+        <v>7004339</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>134217645</v>
       </c>
       <c r="B18" t="n">
-        <v>92389</v>
+        <v>92391</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>134225058</v>
       </c>
       <c r="B21" t="n">
-        <v>80478</v>
+        <v>80479</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>134225054</v>
       </c>
       <c r="B22" t="n">
-        <v>83335</v>
+        <v>83336</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>134217627</v>
       </c>
       <c r="B23" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 20804-2026 artfynd.xlsx
+++ b/artfynd/A 20804-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134225054</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217640</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134225059</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217641</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1199,6 +1224,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217645</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1310,6 +1340,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217642</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1417,6 +1452,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217627</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1524,6 +1564,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217631</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1631,6 +1676,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217638</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1728,6 +1778,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134225057</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1825,6 +1880,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134225062</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1922,6 +1982,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134225058</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2033,6 +2098,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217635</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2130,6 +2200,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134225052</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2227,6 +2302,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134225053</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2342,6 +2422,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217632</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2457,6 +2542,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217636</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2572,6 +2662,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217637</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2687,6 +2782,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217639</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2802,6 +2902,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217628</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2921,6 +3026,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217644</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3028,6 +3138,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217633</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3140,6 +3255,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217626</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3252,8 +3372,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134217634</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>